--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -1068,7 +1068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
@@ -1082,44 +1082,38 @@
     </row>
     <row r="2" s="3" customFormat="1" spans="1:2">
       <c r="A2" s="1">
-        <v>123464203</v>
+        <v>112637865</v>
       </c>
       <c r="B2"/>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:2">
       <c r="A3" s="1">
-        <v>112233962</v>
+        <v>3612824850</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:2">
       <c r="A4" s="1">
-        <v>112637865</v>
+        <v>6260094048</v>
       </c>
       <c r="B4"/>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:2">
       <c r="A5" s="1">
-        <v>3612824850</v>
+        <v>406757605</v>
       </c>
       <c r="B5"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:2">
       <c r="A6" s="1">
-        <v>6260094048</v>
+        <v>1014069758</v>
       </c>
       <c r="B6"/>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:2">
-      <c r="A7" s="1">
-        <v>406757605</v>
-      </c>
       <c r="B7"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:2">
-      <c r="A8" s="1">
-        <v>1014069758</v>
-      </c>
       <c r="B8"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:2">
@@ -1127,7 +1121,6 @@
       <c r="B9"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:2">
-      <c r="A10" s="2"/>
       <c r="B10"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:2">
@@ -1191,11 +1184,11 @@
       <c r="B25"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:2">
-      <c r="A26" s="4"/>
+      <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:2">
-      <c r="A27" s="2"/>
+      <c r="A27" s="4"/>
       <c r="B27"/>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:2">
@@ -1322,12 +1315,15 @@
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A8">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A2:A6">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2249,6 +2245,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="1">
+        <v>123464203</v>
+      </c>
+    </row>
     <row r="190" spans="1:1">
       <c r="A190"/>
     </row>
@@ -2311,8 +2312,11 @@
       <c r="A207" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A189 A197:A1048576">
+  <conditionalFormatting sqref="A188">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A187 A189 A197:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="19635" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>zxy0920</t>
+  </si>
+  <si>
+    <t>wyh111666</t>
+  </si>
+  <si>
+    <t>gzby0816</t>
+  </si>
+  <si>
+    <t>MichaeILiang056</t>
+  </si>
+  <si>
+    <t>axiaobing8899</t>
+  </si>
+  <si>
+    <t>pickle_XR</t>
+  </si>
+  <si>
+    <t>JPirit</t>
+  </si>
+  <si>
     <t>546543612w</t>
   </si>
   <si>
@@ -104,15 +125,6 @@
   </si>
   <si>
     <t>LIZHUORUI618</t>
-  </si>
-  <si>
-    <t>MichaeILiang056</t>
-  </si>
-  <si>
-    <t>axiaobing8899</t>
-  </si>
-  <si>
-    <t>zxy0920</t>
   </si>
 </sst>
 </file>
@@ -125,8 +137,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -598,137 +618,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -737,6 +757,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1074,244 +1097,275 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:2">
+    <row r="1" s="4" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:2">
+    <row r="2" s="4" customFormat="1" spans="1:2">
       <c r="A2" s="1">
-        <v>112637865</v>
+        <v>181070446</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:2">
+    <row r="3" s="4" customFormat="1" spans="1:2">
       <c r="A3" s="1">
-        <v>3612824850</v>
+        <v>874453196</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:2">
-      <c r="A4" s="1">
-        <v>6260094048</v>
+    <row r="4" s="4" customFormat="1" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:2">
+    <row r="5" s="4" customFormat="1" spans="1:2">
       <c r="A5" s="1">
-        <v>406757605</v>
+        <v>6167222127</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:2">
+    <row r="6" s="4" customFormat="1" spans="1:2">
       <c r="A6" s="1">
-        <v>1014069758</v>
+        <v>4951118353</v>
       </c>
       <c r="B6"/>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:2">
+    <row r="7" s="4" customFormat="1" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B7"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:2">
+    <row r="8" s="4" customFormat="1" spans="1:2">
+      <c r="A8" s="1">
+        <v>983081420</v>
+      </c>
       <c r="B8"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:2">
-      <c r="A9" s="2"/>
+    <row r="9" s="4" customFormat="1" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B9"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:2">
+    <row r="10" s="4" customFormat="1" spans="1:2">
+      <c r="A10" s="1">
+        <v>486956361</v>
+      </c>
       <c r="B10"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:2">
-      <c r="A11" s="2"/>
+    <row r="11" s="4" customFormat="1" spans="1:2">
+      <c r="A11" s="1">
+        <v>123464203</v>
+      </c>
       <c r="B11"/>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:2">
-      <c r="A12" s="2"/>
+    <row r="12" s="4" customFormat="1" spans="1:2">
+      <c r="A12" s="1">
+        <v>112233962</v>
+      </c>
       <c r="B12"/>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:2">
-      <c r="A13" s="2"/>
+    <row r="13" s="4" customFormat="1" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="B13"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:2">
-      <c r="A14" s="2"/>
+    <row r="14" s="4" customFormat="1" spans="1:2">
+      <c r="A14" s="1">
+        <v>955891226</v>
+      </c>
       <c r="B14"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:2">
-      <c r="A15" s="2"/>
+    <row r="15" s="4" customFormat="1" spans="1:2">
+      <c r="A15" s="1">
+        <v>428840008</v>
+      </c>
       <c r="B15"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:2">
-      <c r="A16" s="2"/>
+    <row r="16" s="4" customFormat="1" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="B16"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:2">
-      <c r="A17" s="2"/>
+    <row r="17" s="4" customFormat="1" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B17"/>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:2">
-      <c r="A18" s="2"/>
+    <row r="18" s="4" customFormat="1" spans="1:2">
+      <c r="A18" s="1">
+        <v>185454787</v>
+      </c>
       <c r="B18"/>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:2">
-      <c r="A19" s="2"/>
+    <row r="19" s="4" customFormat="1" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B19"/>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:2">
-      <c r="A20" s="2"/>
+    <row r="20" s="4" customFormat="1" spans="1:2">
+      <c r="A20" s="1">
+        <v>946419663</v>
+      </c>
       <c r="B20"/>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:2">
+    <row r="21" s="4" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:2">
+    <row r="22" s="4" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="3" customFormat="1" spans="1:2">
+    <row r="23" s="4" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:2">
+    <row r="24" s="4" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:2">
+    <row r="25" s="4" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:2">
+    <row r="26" s="4" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:2">
-      <c r="A27" s="4"/>
+    <row r="27" s="4" customFormat="1" spans="1:2">
+      <c r="A27" s="5"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:2">
+    <row r="28" s="4" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="3" customFormat="1" spans="1:2">
+    <row r="29" s="4" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="3" customFormat="1" spans="1:2">
+    <row r="30" s="4" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="3" customFormat="1" spans="1:2">
+    <row r="31" s="4" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="3" customFormat="1" spans="1:2">
+    <row r="32" s="4" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:2">
+    <row r="33" s="4" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="3" customFormat="1" spans="1:2">
+    <row r="34" s="4" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="3" customFormat="1" spans="1:2">
+    <row r="35" s="4" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="3" customFormat="1" spans="1:2">
+    <row r="36" s="4" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="3" customFormat="1" spans="1:2">
+    <row r="37" s="4" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="3" customFormat="1" spans="1:2">
+    <row r="38" s="4" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="3" customFormat="1" spans="1:2">
+    <row r="39" s="4" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="3" customFormat="1" spans="1:2">
+    <row r="40" s="4" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="3" customFormat="1" spans="1:2">
+    <row r="41" s="4" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="3" customFormat="1" spans="1:2">
+    <row r="42" s="4" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="3" customFormat="1" spans="1:2">
+    <row r="43" s="4" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="3" customFormat="1" spans="1:2">
+    <row r="44" s="4" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="3" customFormat="1" spans="1:2">
+    <row r="45" s="4" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="3" customFormat="1" spans="1:2">
+    <row r="46" s="4" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="3" customFormat="1" spans="1:2">
+    <row r="47" s="4" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="3" customFormat="1" spans="1:2">
+    <row r="48" s="4" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="3" customFormat="1" spans="1:2">
+    <row r="49" s="4" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="3" customFormat="1" spans="1:2">
+    <row r="50" s="4" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="3" customFormat="1" spans="1:2">
+    <row r="51" s="4" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="3" customFormat="1" spans="1:2">
+    <row r="52" s="4" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="3" customFormat="1" spans="1:2">
+    <row r="53" s="4" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="3" customFormat="1" spans="1:2">
+    <row r="54" s="4" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="3" customFormat="1" spans="1:2">
+    <row r="55" s="4" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="3" customFormat="1" spans="1:2">
+    <row r="56" s="4" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="3" customFormat="1" spans="1:2">
+    <row r="57" s="4" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="3" customFormat="1" spans="1:2">
+    <row r="58" s="4" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1320,9 +1374,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A6">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:A8 A10">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1334,7 +1397,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A207"/>
+  <dimension ref="A1:A208"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.8666666666667" style="1" customWidth="1"/>
@@ -1357,7 +1420,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1377,7 +1440,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1412,7 +1475,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1422,7 +1485,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1442,7 +1505,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1542,7 +1605,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1612,7 +1675,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1647,12 +1710,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1672,7 +1735,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1717,7 +1780,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1747,7 +1810,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1762,7 +1825,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1777,7 +1840,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1826,8 +1889,8 @@
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="5" t="s">
-        <v>15</v>
+      <c r="A98" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1842,7 +1905,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1877,12 +1940,12 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -1897,7 +1960,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -1952,7 +2015,7 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:1">
@@ -2027,7 +2090,7 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -2117,7 +2180,7 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:1">
@@ -2127,7 +2190,7 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:1">
@@ -2197,7 +2260,7 @@
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -2225,97 +2288,131 @@
         <v>398192040</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="1">
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="1">
         <v>955891226</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="1">
+    <row r="186" spans="1:1">
+      <c r="A186" s="1">
         <v>428840008</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="1" t="s">
-        <v>26</v>
+    <row r="187" spans="1:1">
+      <c r="A187" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="1">
-        <v>123464203</v>
+      <c r="A188" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1">
+        <v>185454787</v>
       </c>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190"/>
+      <c r="A190" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="191" spans="1:1">
-      <c r="A191"/>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192"/>
+      <c r="A191" s="1">
+        <v>946419663</v>
+      </c>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193"/>
+      <c r="A193" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="194" spans="1:1">
-      <c r="A194"/>
+      <c r="A194" s="1">
+        <v>983081420</v>
+      </c>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195"/>
+      <c r="A195" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196"/>
+      <c r="A196" s="1">
+        <v>486956361</v>
+      </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="1">
-        <v>181070446</v>
+        <v>123464203</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1">
+        <v>112233962</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="3">
+        <v>112637865</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="3">
+        <v>3612824850</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="3">
+        <v>6260094048</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="3">
+        <v>406757605</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="3">
+        <v>1014069758</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="1">
+        <v>181070446</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="1">
         <v>874453196</v>
       </c>
     </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" s="1">
+    <row r="206" spans="1:1">
+      <c r="A206" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="1">
         <v>6167222127</v>
       </c>
     </row>
-    <row r="201" spans="1:1">
-      <c r="A201" s="1">
+    <row r="208" spans="1:1">
+      <c r="A208" s="1">
         <v>4951118353</v>
       </c>
     </row>
-    <row r="203" spans="1:1">
-      <c r="A203" s="2"/>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" s="2"/>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" s="2"/>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" s="2"/>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" s="2"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A188">
+  <conditionalFormatting sqref="A195">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A187 A189 A197:A1048576">
+  <conditionalFormatting sqref="A1:A177 A184:A191 A193:A194 A196 A204:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2327,9 +2424,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="B6:B10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="2:2">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B6:B10">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7575"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,102 +29,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>546543612w</t>
+  </si>
+  <si>
+    <t>Gw05161108</t>
+  </si>
+  <si>
+    <t>YXHDUSHUHUI</t>
+  </si>
+  <si>
+    <t>xxslly</t>
+  </si>
+  <si>
+    <t>KIRAjia1125</t>
+  </si>
+  <si>
+    <t>Xin06210730</t>
+  </si>
+  <si>
+    <t>030723m</t>
+  </si>
+  <si>
+    <t>yaqian99</t>
+  </si>
+  <si>
+    <t>Coco0201</t>
+  </si>
+  <si>
+    <t>Feng_yy</t>
+  </si>
+  <si>
+    <t>babyjing0915</t>
+  </si>
+  <si>
+    <t>C_OLE99</t>
+  </si>
+  <si>
+    <t>Krystal0628JJ</t>
+  </si>
+  <si>
+    <t>w623726751</t>
+  </si>
+  <si>
+    <t>8290199110520</t>
+  </si>
+  <si>
+    <t>yanjiali</t>
+  </si>
+  <si>
+    <t>crisriverguo</t>
+  </si>
+  <si>
+    <t>Blackcat_ss</t>
+  </si>
+  <si>
+    <t>wanghezhen410</t>
+  </si>
+  <si>
+    <t>yy53445690</t>
+  </si>
+  <si>
+    <t>gy24703</t>
+  </si>
+  <si>
+    <t>Xingfu_2014</t>
+  </si>
+  <si>
+    <t>v18636718996</t>
+  </si>
+  <si>
+    <t>LIZHUORUI618</t>
+  </si>
+  <si>
+    <t>MichaeILiang056</t>
+  </si>
+  <si>
+    <t>axiaobing8899</t>
+  </si>
+  <si>
+    <t>pickle_XR</t>
+  </si>
+  <si>
+    <t>JPirit</t>
+  </si>
+  <si>
+    <t>wyh111666</t>
+  </si>
+  <si>
+    <t>gzby0816</t>
+  </si>
+  <si>
     <t>zxy0920</t>
-  </si>
-  <si>
-    <t>wyh111666</t>
-  </si>
-  <si>
-    <t>gzby0816</t>
-  </si>
-  <si>
-    <t>MichaeILiang056</t>
-  </si>
-  <si>
-    <t>axiaobing8899</t>
-  </si>
-  <si>
-    <t>pickle_XR</t>
-  </si>
-  <si>
-    <t>JPirit</t>
-  </si>
-  <si>
-    <t>546543612w</t>
-  </si>
-  <si>
-    <t>Gw05161108</t>
-  </si>
-  <si>
-    <t>YXHDUSHUHUI</t>
-  </si>
-  <si>
-    <t>xxslly</t>
-  </si>
-  <si>
-    <t>KIRAjia1125</t>
-  </si>
-  <si>
-    <t>Xin06210730</t>
-  </si>
-  <si>
-    <t>030723m</t>
-  </si>
-  <si>
-    <t>yaqian99</t>
-  </si>
-  <si>
-    <t>Coco0201</t>
-  </si>
-  <si>
-    <t>Feng_yy</t>
-  </si>
-  <si>
-    <t>babyjing0915</t>
-  </si>
-  <si>
-    <t>C_OLE99</t>
-  </si>
-  <si>
-    <t>Krystal0628JJ</t>
-  </si>
-  <si>
-    <t>w623726751</t>
-  </si>
-  <si>
-    <t>8290199110520</t>
-  </si>
-  <si>
-    <t>yanjiali</t>
-  </si>
-  <si>
-    <t>crisriverguo</t>
-  </si>
-  <si>
-    <t>Blackcat_ss</t>
-  </si>
-  <si>
-    <t>wanghezhen410</t>
-  </si>
-  <si>
-    <t>yy53445690</t>
-  </si>
-  <si>
-    <t>gy24703</t>
-  </si>
-  <si>
-    <t>Xingfu_2014</t>
-  </si>
-  <si>
-    <t>v18636718996</t>
-  </si>
-  <si>
-    <t>LIZHUORUI618</t>
   </si>
 </sst>
 </file>
@@ -298,12 +298,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -624,7 +636,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -648,16 +660,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -666,89 +678,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -759,6 +771,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -1097,275 +1115,249 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:2">
+    <row r="1" s="6" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="4" customFormat="1" spans="1:2">
-      <c r="A2" s="1">
-        <v>181070446</v>
+    <row r="2" s="6" customFormat="1" spans="1:2">
+      <c r="A2" s="3">
+        <v>710203657</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" s="4" customFormat="1" spans="1:2">
-      <c r="A3" s="1">
-        <v>874453196</v>
+    <row r="3" s="6" customFormat="1" spans="1:2">
+      <c r="A3" s="3">
+        <v>254778375</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" s="4" customFormat="1" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+    <row r="4" s="6" customFormat="1" spans="1:2">
+      <c r="A4" s="3">
+        <v>401175349</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" s="4" customFormat="1" spans="1:2">
-      <c r="A5" s="1">
-        <v>6167222127</v>
+    <row r="5" s="6" customFormat="1" spans="1:2">
+      <c r="A5" s="3">
+        <v>673946666</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" s="4" customFormat="1" spans="1:2">
-      <c r="A6" s="1">
-        <v>4951118353</v>
+    <row r="6" s="6" customFormat="1" spans="1:2">
+      <c r="A6" s="3">
+        <v>113210862</v>
       </c>
       <c r="B6"/>
     </row>
-    <row r="7" s="4" customFormat="1" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
+    <row r="7" s="6" customFormat="1" spans="1:2">
+      <c r="A7" s="3">
+        <v>908902438</v>
       </c>
       <c r="B7"/>
     </row>
-    <row r="8" s="4" customFormat="1" spans="1:2">
-      <c r="A8" s="1">
-        <v>983081420</v>
-      </c>
+    <row r="8" s="6" customFormat="1" spans="1:2">
+      <c r="A8" s="1"/>
       <c r="B8"/>
     </row>
-    <row r="9" s="4" customFormat="1" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
+    <row r="9" s="6" customFormat="1" spans="1:2">
+      <c r="A9" s="1"/>
       <c r="B9"/>
     </row>
-    <row r="10" s="4" customFormat="1" spans="1:2">
-      <c r="A10" s="1">
-        <v>486956361</v>
-      </c>
+    <row r="10" s="6" customFormat="1" spans="1:2">
+      <c r="A10" s="1"/>
       <c r="B10"/>
     </row>
-    <row r="11" s="4" customFormat="1" spans="1:2">
-      <c r="A11" s="1">
-        <v>123464203</v>
-      </c>
+    <row r="11" s="6" customFormat="1" spans="1:2">
+      <c r="A11" s="1"/>
       <c r="B11"/>
     </row>
-    <row r="12" s="4" customFormat="1" spans="1:2">
-      <c r="A12" s="1">
-        <v>112233962</v>
-      </c>
+    <row r="12" s="6" customFormat="1" spans="1:2">
+      <c r="A12" s="1"/>
       <c r="B12"/>
     </row>
-    <row r="13" s="4" customFormat="1" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>4</v>
-      </c>
+    <row r="13" s="6" customFormat="1" spans="1:2">
+      <c r="A13" s="1"/>
       <c r="B13"/>
     </row>
-    <row r="14" s="4" customFormat="1" spans="1:2">
-      <c r="A14" s="1">
-        <v>955891226</v>
-      </c>
+    <row r="14" s="6" customFormat="1" spans="1:2">
+      <c r="A14" s="1"/>
       <c r="B14"/>
     </row>
-    <row r="15" s="4" customFormat="1" spans="1:2">
-      <c r="A15" s="1">
-        <v>428840008</v>
-      </c>
+    <row r="15" s="6" customFormat="1" spans="1:2">
+      <c r="A15" s="1"/>
       <c r="B15"/>
     </row>
-    <row r="16" s="4" customFormat="1" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="16" s="6" customFormat="1" spans="1:2">
+      <c r="A16" s="1"/>
       <c r="B16"/>
     </row>
-    <row r="17" s="4" customFormat="1" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" s="6" customFormat="1" spans="1:2">
+      <c r="A17" s="1"/>
       <c r="B17"/>
     </row>
-    <row r="18" s="4" customFormat="1" spans="1:2">
-      <c r="A18" s="1">
-        <v>185454787</v>
-      </c>
+    <row r="18" s="6" customFormat="1" spans="1:2">
+      <c r="A18" s="1"/>
       <c r="B18"/>
     </row>
-    <row r="19" s="4" customFormat="1" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
+    <row r="19" s="6" customFormat="1" spans="1:2">
+      <c r="A19" s="1"/>
       <c r="B19"/>
     </row>
-    <row r="20" s="4" customFormat="1" spans="1:2">
-      <c r="A20" s="1">
-        <v>946419663</v>
-      </c>
+    <row r="20" s="6" customFormat="1" spans="1:2">
+      <c r="A20" s="1"/>
       <c r="B20"/>
     </row>
-    <row r="21" s="4" customFormat="1" spans="1:2">
+    <row r="21" s="6" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="4" customFormat="1" spans="1:2">
+    <row r="22" s="6" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="4" customFormat="1" spans="1:2">
+    <row r="23" s="6" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="4" customFormat="1" spans="1:2">
+    <row r="24" s="6" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="4" customFormat="1" spans="1:2">
+    <row r="25" s="6" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="4" customFormat="1" spans="1:2">
+    <row r="26" s="6" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="4" customFormat="1" spans="1:2">
-      <c r="A27" s="5"/>
+    <row r="27" s="6" customFormat="1" spans="1:2">
+      <c r="A27" s="7"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="4" customFormat="1" spans="1:2">
+    <row r="28" s="6" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="4" customFormat="1" spans="1:2">
+    <row r="29" s="6" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="4" customFormat="1" spans="1:2">
+    <row r="30" s="6" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="4" customFormat="1" spans="1:2">
+    <row r="31" s="6" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="4" customFormat="1" spans="1:2">
+    <row r="32" s="6" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="4" customFormat="1" spans="1:2">
+    <row r="33" s="6" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="4" customFormat="1" spans="1:2">
+    <row r="34" s="6" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="4" customFormat="1" spans="1:2">
+    <row r="35" s="6" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="4" customFormat="1" spans="1:2">
+    <row r="36" s="6" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="4" customFormat="1" spans="1:2">
+    <row r="37" s="6" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="4" customFormat="1" spans="1:2">
+    <row r="38" s="6" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="4" customFormat="1" spans="1:2">
+    <row r="39" s="6" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="4" customFormat="1" spans="1:2">
+    <row r="40" s="6" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="4" customFormat="1" spans="1:2">
+    <row r="41" s="6" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="4" customFormat="1" spans="1:2">
+    <row r="42" s="6" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="4" customFormat="1" spans="1:2">
+    <row r="43" s="6" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="4" customFormat="1" spans="1:2">
+    <row r="44" s="6" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="4" customFormat="1" spans="1:2">
+    <row r="45" s="6" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="4" customFormat="1" spans="1:2">
+    <row r="46" s="6" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="4" customFormat="1" spans="1:2">
+    <row r="47" s="6" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="4" customFormat="1" spans="1:2">
+    <row r="48" s="6" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="4" customFormat="1" spans="1:2">
+    <row r="49" s="6" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="4" customFormat="1" spans="1:2">
+    <row r="50" s="6" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="4" customFormat="1" spans="1:2">
+    <row r="51" s="6" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="4" customFormat="1" spans="1:2">
+    <row r="52" s="6" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="4" customFormat="1" spans="1:2">
+    <row r="53" s="6" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="4" customFormat="1" spans="1:2">
+    <row r="54" s="6" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="4" customFormat="1" spans="1:2">
+    <row r="55" s="6" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="4" customFormat="1" spans="1:2">
+    <row r="56" s="6" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="4" customFormat="1" spans="1:2">
+    <row r="57" s="6" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="4" customFormat="1" spans="1:2">
+    <row r="58" s="6" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1374,19 +1366,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A7">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A20">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A8 A10">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A8 A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1397,7 +1389,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A208"/>
+  <dimension ref="A1:A207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.8666666666667" style="1" customWidth="1"/>
@@ -1420,7 +1412,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1440,7 +1432,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1475,7 +1467,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1485,7 +1477,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1505,7 +1497,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1605,7 +1597,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1675,7 +1667,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1710,12 +1702,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1735,7 +1727,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1780,7 +1772,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1810,7 +1802,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1825,7 +1817,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1840,7 +1832,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1889,8 +1881,8 @@
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
+      <c r="A98" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1905,7 +1897,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1940,12 +1932,12 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -1960,7 +1952,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2015,7 +2007,7 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:1">
@@ -2090,7 +2082,7 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -2180,7 +2172,7 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:1">
@@ -2190,7 +2182,7 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:1">
@@ -2219,32 +2211,32 @@
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="1">
+      <c r="A164" s="3">
         <v>710203657</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="1">
+      <c r="A165" s="3">
         <v>254778375</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="1">
+      <c r="A166" s="3">
         <v>401175349</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="1">
+      <c r="A167" s="3">
         <v>673946666</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="1">
+      <c r="A168" s="3">
         <v>113210862</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="1">
+      <c r="A169" s="3">
         <v>908902438</v>
       </c>
     </row>
@@ -2260,7 +2252,7 @@
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -2288,132 +2280,150 @@
         <v>398192040</v>
       </c>
     </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="1">
+        <v>955891226</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="1">
+        <v>428840008</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="4">
+        <v>185454787</v>
+      </c>
+    </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="1" t="s">
-        <v>4</v>
+      <c r="A184" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="1">
-        <v>955891226</v>
+      <c r="A185" s="4">
+        <v>946419663</v>
       </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="1">
-        <v>428840008</v>
+      <c r="A186" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="1" t="s">
-        <v>5</v>
+      <c r="A187" s="4">
+        <v>983081420</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="1" t="s">
-        <v>6</v>
+      <c r="A188" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="1">
-        <v>185454787</v>
+      <c r="A189" s="4">
+        <v>486956361</v>
       </c>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190" s="1" t="s">
-        <v>7</v>
+      <c r="A190" s="1">
+        <v>123464203</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="1">
-        <v>946419663</v>
+        <v>112233962</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1">
+        <v>112637865</v>
       </c>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193" s="1" t="s">
-        <v>2</v>
+      <c r="A193" s="1">
+        <v>3612824850</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1">
-        <v>983081420</v>
+        <v>6260094048</v>
       </c>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="1" t="s">
-        <v>3</v>
+      <c r="A195" s="1">
+        <v>406757605</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="1">
-        <v>486956361</v>
+        <v>1014069758</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="1">
-        <v>123464203</v>
+        <v>181070446</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1">
-        <v>112233962</v>
+        <v>874453196</v>
       </c>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="3">
-        <v>112637865</v>
+      <c r="A199" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="3">
-        <v>3612824850</v>
+      <c r="A200" s="1">
+        <v>6167222127</v>
       </c>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="3">
-        <v>6260094048</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="3">
-        <v>406757605</v>
+      <c r="A201" s="1">
+        <v>4951118353</v>
       </c>
     </row>
     <row r="203" spans="1:1">
-      <c r="A203" s="3">
-        <v>1014069758</v>
-      </c>
+      <c r="A203" s="2"/>
     </row>
     <row r="204" spans="1:1">
-      <c r="A204" s="1">
-        <v>181070446</v>
-      </c>
+      <c r="A204" s="2"/>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="1">
-        <v>874453196</v>
-      </c>
+      <c r="A205" s="2"/>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A206" s="2"/>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="1">
-        <v>6167222127</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="1">
-        <v>4951118353</v>
-      </c>
+      <c r="A207" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A195">
+  <conditionalFormatting sqref="A184:A185">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A177 A184:A191 A193:A194 A196 A204:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="A1:A177 A187:A190 A196 A204:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A179:A183 A186">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -29,11 +29,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>Xingfu_2014</t>
+  </si>
+  <si>
+    <t>v18636718996</t>
+  </si>
+  <si>
     <t>546543612w</t>
   </si>
   <si>
@@ -95,12 +101,6 @@
   </si>
   <si>
     <t>gy24703</t>
-  </si>
-  <si>
-    <t>Xingfu_2014</t>
-  </si>
-  <si>
-    <t>v18636718996</t>
   </si>
   <si>
     <t>LIZHUORUI618</t>
@@ -760,7 +760,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -771,6 +771,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1115,249 +1121,257 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:2">
+    <row r="1" s="8" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="6" customFormat="1" spans="1:2">
+    <row r="2" s="8" customFormat="1" spans="1:2">
       <c r="A2" s="3">
-        <v>710203657</v>
+        <v>831999359</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" s="6" customFormat="1" spans="1:2">
+    <row r="3" s="8" customFormat="1" spans="1:2">
       <c r="A3" s="3">
-        <v>254778375</v>
+        <v>26483210886</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" s="6" customFormat="1" spans="1:2">
-      <c r="A4" s="3">
-        <v>401175349</v>
+    <row r="4" s="8" customFormat="1" spans="1:2">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" s="6" customFormat="1" spans="1:2">
+    <row r="5" s="8" customFormat="1" spans="1:2">
       <c r="A5" s="3">
-        <v>673946666</v>
+        <v>420219798</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" s="6" customFormat="1" spans="1:2">
-      <c r="A6" s="3">
-        <v>113210862</v>
+    <row r="6" s="8" customFormat="1" spans="1:2">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="B6"/>
     </row>
-    <row r="7" s="6" customFormat="1" spans="1:2">
+    <row r="7" s="8" customFormat="1" spans="1:2">
       <c r="A7" s="3">
-        <v>908902438</v>
+        <v>121258041</v>
       </c>
       <c r="B7"/>
     </row>
-    <row r="8" s="6" customFormat="1" spans="1:2">
-      <c r="A8" s="1"/>
+    <row r="8" s="8" customFormat="1" spans="1:2">
+      <c r="A8" s="3">
+        <v>1030176304</v>
+      </c>
       <c r="B8"/>
     </row>
-    <row r="9" s="6" customFormat="1" spans="1:2">
-      <c r="A9" s="1"/>
+    <row r="9" s="8" customFormat="1" spans="1:2">
+      <c r="A9" s="3">
+        <v>95379423221</v>
+      </c>
       <c r="B9"/>
     </row>
-    <row r="10" s="6" customFormat="1" spans="1:2">
-      <c r="A10" s="1"/>
+    <row r="10" s="8" customFormat="1" spans="1:2">
+      <c r="A10" s="3">
+        <v>608319777</v>
+      </c>
       <c r="B10"/>
     </row>
-    <row r="11" s="6" customFormat="1" spans="1:2">
-      <c r="A11" s="1"/>
+    <row r="11" s="8" customFormat="1" spans="1:2">
+      <c r="A11" s="3">
+        <v>26502467990</v>
+      </c>
       <c r="B11"/>
     </row>
-    <row r="12" s="6" customFormat="1" spans="1:2">
+    <row r="12" s="8" customFormat="1" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12"/>
     </row>
-    <row r="13" s="6" customFormat="1" spans="1:2">
+    <row r="13" s="8" customFormat="1" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13"/>
     </row>
-    <row r="14" s="6" customFormat="1" spans="1:2">
+    <row r="14" s="8" customFormat="1" spans="1:2">
       <c r="A14" s="1"/>
       <c r="B14"/>
     </row>
-    <row r="15" s="6" customFormat="1" spans="1:2">
+    <row r="15" s="8" customFormat="1" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15"/>
     </row>
-    <row r="16" s="6" customFormat="1" spans="1:2">
+    <row r="16" s="8" customFormat="1" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16"/>
     </row>
-    <row r="17" s="6" customFormat="1" spans="1:2">
+    <row r="17" s="8" customFormat="1" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17"/>
     </row>
-    <row r="18" s="6" customFormat="1" spans="1:2">
+    <row r="18" s="8" customFormat="1" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18"/>
     </row>
-    <row r="19" s="6" customFormat="1" spans="1:2">
+    <row r="19" s="8" customFormat="1" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19"/>
     </row>
-    <row r="20" s="6" customFormat="1" spans="1:2">
+    <row r="20" s="8" customFormat="1" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20"/>
     </row>
-    <row r="21" s="6" customFormat="1" spans="1:2">
+    <row r="21" s="8" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="6" customFormat="1" spans="1:2">
+    <row r="22" s="8" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="6" customFormat="1" spans="1:2">
+    <row r="23" s="8" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="6" customFormat="1" spans="1:2">
+    <row r="24" s="8" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="6" customFormat="1" spans="1:2">
+    <row r="25" s="8" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="6" customFormat="1" spans="1:2">
+    <row r="26" s="8" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="6" customFormat="1" spans="1:2">
-      <c r="A27" s="7"/>
+    <row r="27" s="8" customFormat="1" spans="1:2">
+      <c r="A27" s="9"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="6" customFormat="1" spans="1:2">
+    <row r="28" s="8" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="6" customFormat="1" spans="1:2">
+    <row r="29" s="8" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="6" customFormat="1" spans="1:2">
+    <row r="30" s="8" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="6" customFormat="1" spans="1:2">
+    <row r="31" s="8" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="6" customFormat="1" spans="1:2">
+    <row r="32" s="8" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="6" customFormat="1" spans="1:2">
+    <row r="33" s="8" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="6" customFormat="1" spans="1:2">
+    <row r="34" s="8" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="6" customFormat="1" spans="1:2">
+    <row r="35" s="8" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="6" customFormat="1" spans="1:2">
+    <row r="36" s="8" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="6" customFormat="1" spans="1:2">
+    <row r="37" s="8" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="6" customFormat="1" spans="1:2">
+    <row r="38" s="8" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="6" customFormat="1" spans="1:2">
+    <row r="39" s="8" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="6" customFormat="1" spans="1:2">
+    <row r="40" s="8" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="6" customFormat="1" spans="1:2">
+    <row r="41" s="8" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="6" customFormat="1" spans="1:2">
+    <row r="42" s="8" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="6" customFormat="1" spans="1:2">
+    <row r="43" s="8" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="6" customFormat="1" spans="1:2">
+    <row r="44" s="8" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="6" customFormat="1" spans="1:2">
+    <row r="45" s="8" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="6" customFormat="1" spans="1:2">
+    <row r="46" s="8" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="6" customFormat="1" spans="1:2">
+    <row r="47" s="8" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="6" customFormat="1" spans="1:2">
+    <row r="48" s="8" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="6" customFormat="1" spans="1:2">
+    <row r="49" s="8" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="6" customFormat="1" spans="1:2">
+    <row r="50" s="8" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="6" customFormat="1" spans="1:2">
+    <row r="51" s="8" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="6" customFormat="1" spans="1:2">
+    <row r="52" s="8" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="6" customFormat="1" spans="1:2">
+    <row r="53" s="8" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="6" customFormat="1" spans="1:2">
+    <row r="54" s="8" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="6" customFormat="1" spans="1:2">
+    <row r="55" s="8" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="6" customFormat="1" spans="1:2">
+    <row r="56" s="8" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="6" customFormat="1" spans="1:2">
+    <row r="57" s="8" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="6" customFormat="1" spans="1:2">
+    <row r="58" s="8" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1366,19 +1380,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8 A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1412,7 +1420,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1432,7 +1440,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1467,7 +1475,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1477,7 +1485,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1497,7 +1505,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1597,7 +1605,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1667,7 +1675,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1702,12 +1710,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1727,7 +1735,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1772,7 +1780,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1802,7 +1810,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1817,7 +1825,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1832,7 +1840,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1881,8 +1889,8 @@
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="8" t="s">
-        <v>15</v>
+      <c r="A98" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1897,7 +1905,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1932,12 +1940,12 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -1952,7 +1960,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2007,7 +2015,7 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:1">
@@ -2082,7 +2090,7 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -2161,82 +2169,82 @@
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="1">
+      <c r="A154" s="3">
         <v>831999359</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="1">
+      <c r="A155" s="3">
         <v>26483210886</v>
       </c>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>22</v>
+      <c r="A156" s="4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="1">
+      <c r="A157" s="3">
         <v>420219798</v>
       </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="1" t="s">
-        <v>23</v>
+      <c r="A158" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="1">
+      <c r="A159" s="3">
         <v>121258041</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="1">
+      <c r="A160" s="3">
         <v>1030176304</v>
       </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="1">
+      <c r="A161" s="3">
         <v>95379423221</v>
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="1">
+      <c r="A162" s="3">
         <v>608319777</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="1">
+      <c r="A163" s="3">
         <v>26502467990</v>
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="3">
+      <c r="A164" s="5">
         <v>710203657</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="3">
+      <c r="A165" s="5">
         <v>254778375</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="3">
+      <c r="A166" s="5">
         <v>401175349</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="3">
+      <c r="A167" s="5">
         <v>673946666</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="3">
+      <c r="A168" s="5">
         <v>113210862</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="3">
+      <c r="A169" s="5">
         <v>908902438</v>
       </c>
     </row>
@@ -2301,42 +2309,42 @@
       </c>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="4">
+      <c r="A183" s="6">
         <v>185454787</v>
       </c>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="4">
+      <c r="A185" s="6">
         <v>946419663</v>
       </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="4">
+      <c r="A187" s="6">
         <v>983081420</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="4">
+      <c r="A189" s="6">
         <v>486956361</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,78 +29,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>546543612w</t>
+  </si>
+  <si>
+    <t>Gw05161108</t>
+  </si>
+  <si>
+    <t>YXHDUSHUHUI</t>
+  </si>
+  <si>
+    <t>xxslly</t>
+  </si>
+  <si>
+    <t>KIRAjia1125</t>
+  </si>
+  <si>
+    <t>Xin06210730</t>
+  </si>
+  <si>
+    <t>030723m</t>
+  </si>
+  <si>
+    <t>yaqian99</t>
+  </si>
+  <si>
+    <t>Coco0201</t>
+  </si>
+  <si>
+    <t>Feng_yy</t>
+  </si>
+  <si>
+    <t>babyjing0915</t>
+  </si>
+  <si>
+    <t>C_OLE99</t>
+  </si>
+  <si>
+    <t>Krystal0628JJ</t>
+  </si>
+  <si>
+    <t>w623726751</t>
+  </si>
+  <si>
+    <t>8290199110520</t>
+  </si>
+  <si>
+    <t>yanjiali</t>
+  </si>
+  <si>
+    <t>crisriverguo</t>
+  </si>
+  <si>
+    <t>Blackcat_ss</t>
+  </si>
+  <si>
+    <t>wanghezhen410</t>
+  </si>
+  <si>
+    <t>yy53445690</t>
+  </si>
+  <si>
+    <t>gy24703</t>
+  </si>
+  <si>
     <t>Xingfu_2014</t>
   </si>
   <si>
     <t>v18636718996</t>
-  </si>
-  <si>
-    <t>546543612w</t>
-  </si>
-  <si>
-    <t>Gw05161108</t>
-  </si>
-  <si>
-    <t>YXHDUSHUHUI</t>
-  </si>
-  <si>
-    <t>xxslly</t>
-  </si>
-  <si>
-    <t>KIRAjia1125</t>
-  </si>
-  <si>
-    <t>Xin06210730</t>
-  </si>
-  <si>
-    <t>030723m</t>
-  </si>
-  <si>
-    <t>yaqian99</t>
-  </si>
-  <si>
-    <t>Coco0201</t>
-  </si>
-  <si>
-    <t>Feng_yy</t>
-  </si>
-  <si>
-    <t>babyjing0915</t>
-  </si>
-  <si>
-    <t>C_OLE99</t>
-  </si>
-  <si>
-    <t>Krystal0628JJ</t>
-  </si>
-  <si>
-    <t>w623726751</t>
-  </si>
-  <si>
-    <t>8290199110520</t>
-  </si>
-  <si>
-    <t>yanjiali</t>
-  </si>
-  <si>
-    <t>crisriverguo</t>
-  </si>
-  <si>
-    <t>Blackcat_ss</t>
-  </si>
-  <si>
-    <t>wanghezhen410</t>
-  </si>
-  <si>
-    <t>yy53445690</t>
-  </si>
-  <si>
-    <t>gy24703</t>
   </si>
   <si>
     <t>LIZHUORUI618</t>
@@ -773,19 +773,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1121,257 +1121,241 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:2">
+    <row r="1" s="7" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:2">
+    <row r="2" s="7" customFormat="1" spans="1:2">
       <c r="A2" s="3">
-        <v>831999359</v>
+        <v>4987552268</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:2">
+    <row r="3" s="7" customFormat="1" spans="1:2">
       <c r="A3" s="3">
-        <v>26483210886</v>
+        <v>266467776</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:2">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
+    <row r="4" s="7" customFormat="1" spans="1:2">
+      <c r="A4" s="1"/>
       <c r="B4"/>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:2">
-      <c r="A5" s="3">
-        <v>420219798</v>
-      </c>
+    <row r="5" s="7" customFormat="1" spans="1:2">
+      <c r="A5" s="8"/>
       <c r="B5"/>
     </row>
-    <row r="6" s="8" customFormat="1" spans="1:2">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
+    <row r="6" s="7" customFormat="1" spans="1:2">
+      <c r="A6" s="8"/>
       <c r="B6"/>
     </row>
-    <row r="7" s="8" customFormat="1" spans="1:2">
-      <c r="A7" s="3">
-        <v>121258041</v>
-      </c>
+    <row r="7" s="7" customFormat="1" spans="1:2">
+      <c r="A7" s="8"/>
       <c r="B7"/>
     </row>
-    <row r="8" s="8" customFormat="1" spans="1:2">
-      <c r="A8" s="3">
-        <v>1030176304</v>
-      </c>
+    <row r="8" s="7" customFormat="1" spans="1:2">
+      <c r="A8" s="8"/>
       <c r="B8"/>
     </row>
-    <row r="9" s="8" customFormat="1" spans="1:2">
-      <c r="A9" s="3">
-        <v>95379423221</v>
-      </c>
+    <row r="9" s="7" customFormat="1" spans="1:2">
+      <c r="A9" s="8"/>
       <c r="B9"/>
     </row>
-    <row r="10" s="8" customFormat="1" spans="1:2">
-      <c r="A10" s="3">
-        <v>608319777</v>
-      </c>
+    <row r="10" s="7" customFormat="1" spans="1:2">
+      <c r="A10" s="8"/>
       <c r="B10"/>
     </row>
-    <row r="11" s="8" customFormat="1" spans="1:2">
-      <c r="A11" s="3">
-        <v>26502467990</v>
-      </c>
+    <row r="11" s="7" customFormat="1" spans="1:2">
+      <c r="A11" s="8"/>
       <c r="B11"/>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:2">
+    <row r="12" s="7" customFormat="1" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12"/>
     </row>
-    <row r="13" s="8" customFormat="1" spans="1:2">
+    <row r="13" s="7" customFormat="1" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13"/>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:2">
+    <row r="14" s="7" customFormat="1" spans="1:2">
       <c r="A14" s="1"/>
       <c r="B14"/>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:2">
+    <row r="15" s="7" customFormat="1" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15"/>
     </row>
-    <row r="16" s="8" customFormat="1" spans="1:2">
+    <row r="16" s="7" customFormat="1" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16"/>
     </row>
-    <row r="17" s="8" customFormat="1" spans="1:2">
+    <row r="17" s="7" customFormat="1" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17"/>
     </row>
-    <row r="18" s="8" customFormat="1" spans="1:2">
+    <row r="18" s="7" customFormat="1" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18"/>
     </row>
-    <row r="19" s="8" customFormat="1" spans="1:2">
+    <row r="19" s="7" customFormat="1" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19"/>
     </row>
-    <row r="20" s="8" customFormat="1" spans="1:2">
+    <row r="20" s="7" customFormat="1" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20"/>
     </row>
-    <row r="21" s="8" customFormat="1" spans="1:2">
+    <row r="21" s="7" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="8" customFormat="1" spans="1:2">
+    <row r="22" s="7" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="8" customFormat="1" spans="1:2">
+    <row r="23" s="7" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="8" customFormat="1" spans="1:2">
+    <row r="24" s="7" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="8" customFormat="1" spans="1:2">
+    <row r="25" s="7" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="8" customFormat="1" spans="1:2">
+    <row r="26" s="7" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="8" customFormat="1" spans="1:2">
+    <row r="27" s="7" customFormat="1" spans="1:2">
       <c r="A27" s="9"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="8" customFormat="1" spans="1:2">
+    <row r="28" s="7" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="8" customFormat="1" spans="1:2">
+    <row r="29" s="7" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="8" customFormat="1" spans="1:2">
+    <row r="30" s="7" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="8" customFormat="1" spans="1:2">
+    <row r="31" s="7" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="8" customFormat="1" spans="1:2">
+    <row r="32" s="7" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="8" customFormat="1" spans="1:2">
+    <row r="33" s="7" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="8" customFormat="1" spans="1:2">
+    <row r="34" s="7" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="8" customFormat="1" spans="1:2">
+    <row r="35" s="7" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="8" customFormat="1" spans="1:2">
+    <row r="36" s="7" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="8" customFormat="1" spans="1:2">
+    <row r="37" s="7" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="8" customFormat="1" spans="1:2">
+    <row r="38" s="7" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="8" customFormat="1" spans="1:2">
+    <row r="39" s="7" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="8" customFormat="1" spans="1:2">
+    <row r="40" s="7" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="8" customFormat="1" spans="1:2">
+    <row r="41" s="7" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="8" customFormat="1" spans="1:2">
+    <row r="42" s="7" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="8" customFormat="1" spans="1:2">
+    <row r="43" s="7" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="8" customFormat="1" spans="1:2">
+    <row r="44" s="7" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="8" customFormat="1" spans="1:2">
+    <row r="45" s="7" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="8" customFormat="1" spans="1:2">
+    <row r="46" s="7" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="8" customFormat="1" spans="1:2">
+    <row r="47" s="7" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="8" customFormat="1" spans="1:2">
+    <row r="48" s="7" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="8" customFormat="1" spans="1:2">
+    <row r="49" s="7" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="8" customFormat="1" spans="1:2">
+    <row r="50" s="7" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="8" customFormat="1" spans="1:2">
+    <row r="51" s="7" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="8" customFormat="1" spans="1:2">
+    <row r="52" s="7" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="8" customFormat="1" spans="1:2">
+    <row r="53" s="7" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="8" customFormat="1" spans="1:2">
+    <row r="54" s="7" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="8" customFormat="1" spans="1:2">
+    <row r="55" s="7" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="8" customFormat="1" spans="1:2">
+    <row r="56" s="7" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="8" customFormat="1" spans="1:2">
+    <row r="57" s="7" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="8" customFormat="1" spans="1:2">
+    <row r="58" s="7" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1380,13 +1364,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A4">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A11">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1420,7 +1410,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1440,7 +1430,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1475,7 +1465,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1485,7 +1475,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1505,7 +1495,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1605,7 +1595,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1675,7 +1665,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1710,12 +1700,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1735,7 +1725,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1780,7 +1770,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1810,7 +1800,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1825,7 +1815,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1840,7 +1830,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1890,7 +1880,7 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1905,7 +1895,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1940,12 +1930,12 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -1960,7 +1950,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2015,7 +2005,7 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:1">
@@ -2090,7 +2080,7 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -2144,107 +2134,107 @@
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="1">
+      <c r="A149" s="3">
         <v>4987552268</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="1">
+      <c r="A150" s="3">
         <v>266467776</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="1">
+      <c r="A151" s="4">
         <v>956080813</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="1">
+      <c r="A152" s="4">
         <v>3499269458</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="1">
+      <c r="A153" s="4">
         <v>95844646387</v>
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="3">
+      <c r="A154" s="4">
         <v>831999359</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="3">
+      <c r="A155" s="4">
         <v>26483210886</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="4" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="3">
+      <c r="A157" s="4">
         <v>420219798</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="4" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="3">
+      <c r="A159" s="4">
         <v>121258041</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="3">
+      <c r="A160" s="4">
         <v>1030176304</v>
       </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="3">
+      <c r="A161" s="4">
         <v>95379423221</v>
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="3">
+      <c r="A162" s="4">
         <v>608319777</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="3">
+      <c r="A163" s="4">
         <v>26502467990</v>
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="5">
+      <c r="A164" s="4">
         <v>710203657</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="5">
+      <c r="A165" s="4">
         <v>254778375</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="5">
+      <c r="A166" s="4">
         <v>401175349</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="5">
+      <c r="A167" s="4">
         <v>673946666</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="5">
+      <c r="A168" s="4">
         <v>113210862</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="5">
+      <c r="A169" s="4">
         <v>908902438</v>
       </c>
     </row>
@@ -2309,42 +2299,42 @@
       </c>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="6">
+      <c r="A183" s="5">
         <v>185454787</v>
       </c>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="7" t="s">
+      <c r="A184" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="6">
+      <c r="A185" s="5">
         <v>946419663</v>
       </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="6">
+      <c r="A187" s="5">
         <v>983081420</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="6">
+      <c r="A189" s="5">
         <v>486956361</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1128,14 +1128,14 @@
       <c r="B1"/>
     </row>
     <row r="2" s="7" customFormat="1" spans="1:2">
-      <c r="A2" s="3">
-        <v>4987552268</v>
+      <c r="A2" s="1">
+        <v>27239501863</v>
       </c>
       <c r="B2"/>
     </row>
     <row r="3" s="7" customFormat="1" spans="1:2">
-      <c r="A3" s="3">
-        <v>266467776</v>
+      <c r="A3" s="1">
+        <v>9497311231</v>
       </c>
       <c r="B3"/>
     </row>
@@ -1364,19 +1364,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2124,22 +2124,22 @@
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="1">
+      <c r="A147" s="3">
         <v>27239501863</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="1">
+      <c r="A148" s="3">
         <v>9497311231</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="3">
+      <c r="A149" s="4">
         <v>4987552268</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="3">
+      <c r="A150" s="4">
         <v>266467776</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="19635" windowHeight="6975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -773,6 +773,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -783,9 +786,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1121,241 +1121,245 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:2">
+    <row r="1" s="8" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="7" customFormat="1" spans="1:2">
-      <c r="A2" s="1">
+    <row r="2" s="8" customFormat="1" spans="1:2">
+      <c r="A2" s="3">
+        <v>49759885232</v>
+      </c>
+      <c r="B2"/>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:2">
+      <c r="A3" s="3">
+        <v>49366701843</v>
+      </c>
+      <c r="B3"/>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:2">
+      <c r="A4" s="4">
         <v>27239501863</v>
       </c>
-      <c r="B2"/>
-    </row>
-    <row r="3" s="7" customFormat="1" spans="1:2">
-      <c r="A3" s="1">
+      <c r="B4"/>
+    </row>
+    <row r="5" s="8" customFormat="1" spans="1:2">
+      <c r="A5" s="4">
         <v>9497311231</v>
       </c>
-      <c r="B3"/>
-    </row>
-    <row r="4" s="7" customFormat="1" spans="1:2">
-      <c r="A4" s="1"/>
-      <c r="B4"/>
-    </row>
-    <row r="5" s="7" customFormat="1" spans="1:2">
-      <c r="A5" s="8"/>
       <c r="B5"/>
     </row>
-    <row r="6" s="7" customFormat="1" spans="1:2">
-      <c r="A6" s="8"/>
+    <row r="6" s="8" customFormat="1" spans="1:2">
+      <c r="A6" s="4"/>
       <c r="B6"/>
     </row>
-    <row r="7" s="7" customFormat="1" spans="1:2">
-      <c r="A7" s="8"/>
+    <row r="7" s="8" customFormat="1" spans="1:2">
+      <c r="A7" s="4"/>
       <c r="B7"/>
     </row>
-    <row r="8" s="7" customFormat="1" spans="1:2">
-      <c r="A8" s="8"/>
+    <row r="8" s="8" customFormat="1" spans="1:2">
+      <c r="A8" s="4"/>
       <c r="B8"/>
     </row>
-    <row r="9" s="7" customFormat="1" spans="1:2">
-      <c r="A9" s="8"/>
+    <row r="9" s="8" customFormat="1" spans="1:2">
+      <c r="A9" s="4"/>
       <c r="B9"/>
     </row>
-    <row r="10" s="7" customFormat="1" spans="1:2">
-      <c r="A10" s="8"/>
+    <row r="10" s="8" customFormat="1" spans="1:2">
+      <c r="A10" s="4"/>
       <c r="B10"/>
     </row>
-    <row r="11" s="7" customFormat="1" spans="1:2">
-      <c r="A11" s="8"/>
+    <row r="11" s="8" customFormat="1" spans="1:2">
+      <c r="A11" s="4"/>
       <c r="B11"/>
     </row>
-    <row r="12" s="7" customFormat="1" spans="1:2">
+    <row r="12" s="8" customFormat="1" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12"/>
     </row>
-    <row r="13" s="7" customFormat="1" spans="1:2">
+    <row r="13" s="8" customFormat="1" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13"/>
     </row>
-    <row r="14" s="7" customFormat="1" spans="1:2">
+    <row r="14" s="8" customFormat="1" spans="1:2">
       <c r="A14" s="1"/>
       <c r="B14"/>
     </row>
-    <row r="15" s="7" customFormat="1" spans="1:2">
+    <row r="15" s="8" customFormat="1" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15"/>
     </row>
-    <row r="16" s="7" customFormat="1" spans="1:2">
+    <row r="16" s="8" customFormat="1" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16"/>
     </row>
-    <row r="17" s="7" customFormat="1" spans="1:2">
+    <row r="17" s="8" customFormat="1" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17"/>
     </row>
-    <row r="18" s="7" customFormat="1" spans="1:2">
+    <row r="18" s="8" customFormat="1" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18"/>
     </row>
-    <row r="19" s="7" customFormat="1" spans="1:2">
+    <row r="19" s="8" customFormat="1" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19"/>
     </row>
-    <row r="20" s="7" customFormat="1" spans="1:2">
+    <row r="20" s="8" customFormat="1" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20"/>
     </row>
-    <row r="21" s="7" customFormat="1" spans="1:2">
+    <row r="21" s="8" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="7" customFormat="1" spans="1:2">
+    <row r="22" s="8" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="7" customFormat="1" spans="1:2">
+    <row r="23" s="8" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="7" customFormat="1" spans="1:2">
+    <row r="24" s="8" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="7" customFormat="1" spans="1:2">
+    <row r="25" s="8" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="7" customFormat="1" spans="1:2">
+    <row r="26" s="8" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="7" customFormat="1" spans="1:2">
+    <row r="27" s="8" customFormat="1" spans="1:2">
       <c r="A27" s="9"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="7" customFormat="1" spans="1:2">
+    <row r="28" s="8" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="7" customFormat="1" spans="1:2">
+    <row r="29" s="8" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="7" customFormat="1" spans="1:2">
+    <row r="30" s="8" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="7" customFormat="1" spans="1:2">
+    <row r="31" s="8" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="7" customFormat="1" spans="1:2">
+    <row r="32" s="8" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="7" customFormat="1" spans="1:2">
+    <row r="33" s="8" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="7" customFormat="1" spans="1:2">
+    <row r="34" s="8" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="7" customFormat="1" spans="1:2">
+    <row r="35" s="8" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="7" customFormat="1" spans="1:2">
+    <row r="36" s="8" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="7" customFormat="1" spans="1:2">
+    <row r="37" s="8" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="7" customFormat="1" spans="1:2">
+    <row r="38" s="8" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="7" customFormat="1" spans="1:2">
+    <row r="39" s="8" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="7" customFormat="1" spans="1:2">
+    <row r="40" s="8" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="7" customFormat="1" spans="1:2">
+    <row r="41" s="8" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="7" customFormat="1" spans="1:2">
+    <row r="42" s="8" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="7" customFormat="1" spans="1:2">
+    <row r="43" s="8" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="7" customFormat="1" spans="1:2">
+    <row r="44" s="8" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="7" customFormat="1" spans="1:2">
+    <row r="45" s="8" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="7" customFormat="1" spans="1:2">
+    <row r="46" s="8" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="7" customFormat="1" spans="1:2">
+    <row r="47" s="8" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="7" customFormat="1" spans="1:2">
+    <row r="48" s="8" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="7" customFormat="1" spans="1:2">
+    <row r="49" s="8" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="7" customFormat="1" spans="1:2">
+    <row r="50" s="8" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="7" customFormat="1" spans="1:2">
+    <row r="51" s="8" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="7" customFormat="1" spans="1:2">
+    <row r="52" s="8" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="7" customFormat="1" spans="1:2">
+    <row r="53" s="8" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="7" customFormat="1" spans="1:2">
+    <row r="54" s="8" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="7" customFormat="1" spans="1:2">
+    <row r="55" s="8" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="7" customFormat="1" spans="1:2">
+    <row r="56" s="8" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="7" customFormat="1" spans="1:2">
+    <row r="57" s="8" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="7" customFormat="1" spans="1:2">
+    <row r="58" s="8" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1364,19 +1368,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="A6:A11">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2114,127 +2115,127 @@
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="1">
+      <c r="A145" s="3">
         <v>49759885232</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="1">
+      <c r="A146" s="3">
         <v>49366701843</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="3">
+      <c r="A147" s="4">
         <v>27239501863</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="3">
+      <c r="A148" s="4">
         <v>9497311231</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="4">
+      <c r="A149" s="5">
         <v>4987552268</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="4">
+      <c r="A150" s="5">
         <v>266467776</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="4">
+      <c r="A151" s="5">
         <v>956080813</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="4">
+      <c r="A152" s="5">
         <v>3499269458</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="4">
+      <c r="A153" s="5">
         <v>95844646387</v>
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="4">
+      <c r="A154" s="5">
         <v>831999359</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="4">
+      <c r="A155" s="5">
         <v>26483210886</v>
       </c>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="4">
+      <c r="A157" s="5">
         <v>420219798</v>
       </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="4">
+      <c r="A159" s="5">
         <v>121258041</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="4">
+      <c r="A160" s="5">
         <v>1030176304</v>
       </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="4">
+      <c r="A161" s="5">
         <v>95379423221</v>
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="4">
+      <c r="A162" s="5">
         <v>608319777</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="4">
+      <c r="A163" s="5">
         <v>26502467990</v>
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="4">
+      <c r="A164" s="5">
         <v>710203657</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="4">
+      <c r="A165" s="5">
         <v>254778375</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="4">
+      <c r="A166" s="5">
         <v>401175349</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="4">
+      <c r="A167" s="5">
         <v>673946666</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="4">
+      <c r="A168" s="5">
         <v>113210862</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="4">
+      <c r="A169" s="5">
         <v>908902438</v>
       </c>
     </row>
@@ -2299,42 +2300,42 @@
       </c>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="5" t="s">
+      <c r="A182" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="5">
+      <c r="A183" s="6">
         <v>185454787</v>
       </c>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="5">
+      <c r="A185" s="6">
         <v>946419663</v>
       </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="5">
+      <c r="A187" s="6">
         <v>983081420</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="5" t="s">
+      <c r="A188" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="5">
+      <c r="A189" s="6">
         <v>486956361</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -1129,26 +1129,24 @@
     </row>
     <row r="2" s="8" customFormat="1" spans="1:2">
       <c r="A2" s="3">
-        <v>49759885232</v>
+        <v>621744185</v>
       </c>
       <c r="B2"/>
     </row>
     <row r="3" s="8" customFormat="1" spans="1:2">
       <c r="A3" s="3">
-        <v>49366701843</v>
+        <v>968050527</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" s="8" customFormat="1" spans="1:2">
-      <c r="A4" s="4">
-        <v>27239501863</v>
+      <c r="A4" s="3">
+        <v>4281272375</v>
       </c>
       <c r="B4"/>
     </row>
     <row r="5" s="8" customFormat="1" spans="1:2">
-      <c r="A5" s="4">
-        <v>9497311231</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5"/>
     </row>
     <row r="6" s="8" customFormat="1" spans="1:2">
@@ -1368,16 +1366,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2060,67 +2061,67 @@
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="1">
+      <c r="A134" s="3">
         <v>621744185</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="1">
+      <c r="A135" s="3">
         <v>968050527</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="1">
+      <c r="A136" s="3">
         <v>4281272375</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="1">
+      <c r="A137" s="3">
         <v>448182922</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="1">
+      <c r="A139" s="3">
         <v>42949055728</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="1">
+      <c r="A140" s="3">
         <v>512106660</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="1">
+      <c r="A141" s="4">
         <v>26268349731</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="1">
+      <c r="A142" s="4">
         <v>63577559672</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="1">
+      <c r="A143" s="4">
         <v>63849369908</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="1">
+      <c r="A144" s="4">
         <v>152183964</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="3">
+      <c r="A145" s="4">
         <v>49759885232</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="3">
+      <c r="A146" s="4">
         <v>49366701843</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -29,11 +29,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>crisriverguo</t>
+  </si>
+  <si>
+    <t>Blackcat_ss</t>
+  </si>
+  <si>
+    <t>wanghezhen410</t>
+  </si>
+  <si>
     <t>546543612w</t>
   </si>
   <si>
@@ -80,15 +89,6 @@
   </si>
   <si>
     <t>yanjiali</t>
-  </si>
-  <si>
-    <t>crisriverguo</t>
-  </si>
-  <si>
-    <t>Blackcat_ss</t>
-  </si>
-  <si>
-    <t>wanghezhen410</t>
   </si>
   <si>
     <t>yy53445690</t>
@@ -1129,48 +1129,62 @@
     </row>
     <row r="2" s="8" customFormat="1" spans="1:2">
       <c r="A2" s="3">
-        <v>621744185</v>
+        <v>895902942</v>
       </c>
       <c r="B2"/>
     </row>
     <row r="3" s="8" customFormat="1" spans="1:2">
       <c r="A3" s="3">
-        <v>968050527</v>
+        <v>4221755217</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" s="8" customFormat="1" spans="1:2">
       <c r="A4" s="3">
-        <v>4281272375</v>
+        <v>1043202493</v>
       </c>
       <c r="B4"/>
     </row>
     <row r="5" s="8" customFormat="1" spans="1:2">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3">
+        <v>104763407</v>
+      </c>
       <c r="B5"/>
     </row>
     <row r="6" s="8" customFormat="1" spans="1:2">
-      <c r="A6" s="4"/>
+      <c r="A6" s="3">
+        <v>924493003</v>
+      </c>
       <c r="B6"/>
     </row>
     <row r="7" s="8" customFormat="1" spans="1:2">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="B7"/>
     </row>
     <row r="8" s="8" customFormat="1" spans="1:2">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="B8"/>
     </row>
     <row r="9" s="8" customFormat="1" spans="1:2">
-      <c r="A9" s="4"/>
+      <c r="A9" s="3">
+        <v>278054850</v>
+      </c>
       <c r="B9"/>
     </row>
     <row r="10" s="8" customFormat="1" spans="1:2">
-      <c r="A10" s="4"/>
+      <c r="A10" s="3">
+        <v>11434582801</v>
+      </c>
       <c r="B10"/>
     </row>
     <row r="11" s="8" customFormat="1" spans="1:2">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="B11"/>
     </row>
     <row r="12" s="8" customFormat="1" spans="1:2">
@@ -1366,19 +1380,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1412,7 +1420,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1432,7 +1440,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1467,7 +1475,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1477,7 +1485,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1497,7 +1505,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1597,7 +1605,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1667,7 +1675,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1702,12 +1710,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1727,7 +1735,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1772,7 +1780,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1802,7 +1810,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1817,7 +1825,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1832,7 +1840,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1882,7 +1890,7 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1897,7 +1905,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1906,177 +1914,177 @@
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="1">
+      <c r="A103" s="3">
         <v>895902942</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="1">
+      <c r="A104" s="3">
         <v>4221755217</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="1">
+      <c r="A105" s="3">
         <v>1043202493</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="1">
+      <c r="A106" s="3">
         <v>104763407</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="1">
+      <c r="A107" s="3">
         <v>924493003</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="1" t="s">
-        <v>17</v>
+      <c r="A108" s="4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="1" t="s">
-        <v>18</v>
+      <c r="A109" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="1">
+      <c r="A110" s="3">
         <v>278054850</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="1">
+      <c r="A111" s="3">
         <v>11434582801</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="1" t="s">
-        <v>19</v>
+      <c r="A112" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="1">
+      <c r="A113" s="3">
         <v>835951263</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="1">
+      <c r="A114" s="3">
         <v>279571969</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="1">
+      <c r="A115" s="3">
         <v>275309654</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="1">
+      <c r="A116" s="3">
         <v>949445670</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="1">
+      <c r="A117" s="3">
         <v>125412788</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="1">
+      <c r="A118" s="3">
         <v>420291280</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="1">
+      <c r="A119" s="3">
         <v>4248688232</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="1">
+      <c r="A120" s="3">
         <v>967213986</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="1">
+      <c r="A121" s="3">
         <v>184554490</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="1">
+      <c r="A122" s="3">
         <v>1189125770</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="1">
+      <c r="A124" s="4">
         <v>432621331</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="1">
+      <c r="A125" s="4">
         <v>493936226</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="1">
+      <c r="A126" s="4">
         <v>4277391745</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="1">
+      <c r="A127" s="4">
         <v>947344441</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="1">
+      <c r="A128" s="4">
         <v>359630325</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="1">
+      <c r="A129" s="4">
         <v>1119329980</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="1">
+      <c r="A130" s="4">
         <v>812069862</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="1">
+      <c r="A131" s="4">
         <v>1078528462</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="1">
+      <c r="A132" s="4">
         <v>6579527673</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="1">
+      <c r="A133" s="4">
         <v>27482161619</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="3">
+      <c r="A134" s="4">
         <v>621744185</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="3">
+      <c r="A135" s="4">
         <v>968050527</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="3">
+      <c r="A136" s="4">
         <v>4281272375</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="3">
+      <c r="A137" s="4">
         <v>448182922</v>
       </c>
     </row>
@@ -2086,12 +2094,12 @@
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="3">
+      <c r="A139" s="4">
         <v>42949055728</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="3">
+      <c r="A140" s="4">
         <v>512106660</v>
       </c>
     </row>

--- a/spider_xhs/第一批200用户2026.6.3.xlsx
+++ b/spider_xhs/第一批200用户2026.6.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="6975"/>
+    <workbookView windowWidth="19635" windowHeight="7575" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>user_id</t>
   </si>
   <si>
+    <t>zxy0920</t>
+  </si>
+  <si>
+    <t>546543612w</t>
+  </si>
+  <si>
+    <t>Gw05161108</t>
+  </si>
+  <si>
+    <t>YXHDUSHUHUI</t>
+  </si>
+  <si>
+    <t>xxslly</t>
+  </si>
+  <si>
+    <t>KIRAjia1125</t>
+  </si>
+  <si>
+    <t>Xin06210730</t>
+  </si>
+  <si>
+    <t>030723m</t>
+  </si>
+  <si>
+    <t>yaqian99</t>
+  </si>
+  <si>
+    <t>Coco0201</t>
+  </si>
+  <si>
+    <t>Feng_yy</t>
+  </si>
+  <si>
+    <t>babyjing0915</t>
+  </si>
+  <si>
+    <t>C_OLE99</t>
+  </si>
+  <si>
+    <t>Krystal0628JJ</t>
+  </si>
+  <si>
+    <t>w623726751</t>
+  </si>
+  <si>
+    <t>8290199110520</t>
+  </si>
+  <si>
+    <t>yanjiali</t>
+  </si>
+  <si>
     <t>crisriverguo</t>
   </si>
   <si>
@@ -43,54 +94,6 @@
     <t>wanghezhen410</t>
   </si>
   <si>
-    <t>546543612w</t>
-  </si>
-  <si>
-    <t>Gw05161108</t>
-  </si>
-  <si>
-    <t>YXHDUSHUHUI</t>
-  </si>
-  <si>
-    <t>xxslly</t>
-  </si>
-  <si>
-    <t>KIRAjia1125</t>
-  </si>
-  <si>
-    <t>Xin06210730</t>
-  </si>
-  <si>
-    <t>030723m</t>
-  </si>
-  <si>
-    <t>yaqian99</t>
-  </si>
-  <si>
-    <t>Coco0201</t>
-  </si>
-  <si>
-    <t>Feng_yy</t>
-  </si>
-  <si>
-    <t>babyjing0915</t>
-  </si>
-  <si>
-    <t>C_OLE99</t>
-  </si>
-  <si>
-    <t>Krystal0628JJ</t>
-  </si>
-  <si>
-    <t>w623726751</t>
-  </si>
-  <si>
-    <t>8290199110520</t>
-  </si>
-  <si>
-    <t>yanjiali</t>
-  </si>
-  <si>
     <t>yy53445690</t>
   </si>
   <si>
@@ -122,9 +125,6 @@
   </si>
   <si>
     <t>gzby0816</t>
-  </si>
-  <si>
-    <t>zxy0920</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -770,19 +770,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -1121,257 +1124,261 @@
     <col min="1" max="1" width="13.0166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:2">
+    <row r="1" s="9" customFormat="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:2">
-      <c r="A2" s="3">
-        <v>895902942</v>
+    <row r="2" s="9" customFormat="1" spans="1:2">
+      <c r="A2" s="1">
+        <v>123464203</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:2">
-      <c r="A3" s="3">
-        <v>4221755217</v>
+    <row r="3" s="9" customFormat="1" spans="1:2">
+      <c r="A3" s="1">
+        <v>112233962</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:2">
-      <c r="A4" s="3">
-        <v>1043202493</v>
+    <row r="4" s="9" customFormat="1" spans="1:2">
+      <c r="A4" s="1">
+        <v>112637865</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:2">
-      <c r="A5" s="3">
-        <v>104763407</v>
+    <row r="5" s="9" customFormat="1" spans="1:2">
+      <c r="A5" s="1">
+        <v>3612824850</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" s="8" customFormat="1" spans="1:2">
-      <c r="A6" s="3">
-        <v>924493003</v>
+    <row r="6" s="9" customFormat="1" spans="1:2">
+      <c r="A6" s="1">
+        <v>6260094048</v>
       </c>
       <c r="B6"/>
     </row>
-    <row r="7" s="8" customFormat="1" spans="1:2">
-      <c r="A7" s="4" t="s">
+    <row r="7" s="9" customFormat="1" spans="1:2">
+      <c r="A7" s="1">
+        <v>406757605</v>
+      </c>
+      <c r="B7"/>
+    </row>
+    <row r="8" s="9" customFormat="1" spans="1:2">
+      <c r="A8" s="1">
+        <v>1014069758</v>
+      </c>
+      <c r="B8"/>
+    </row>
+    <row r="9" s="9" customFormat="1" spans="1:2">
+      <c r="A9" s="1">
+        <v>181070446</v>
+      </c>
+      <c r="B9"/>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:2">
+      <c r="A10" s="1">
+        <v>874453196</v>
+      </c>
+      <c r="B10"/>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:2">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7"/>
-    </row>
-    <row r="8" s="8" customFormat="1" spans="1:2">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8"/>
-    </row>
-    <row r="9" s="8" customFormat="1" spans="1:2">
-      <c r="A9" s="3">
-        <v>278054850</v>
-      </c>
-      <c r="B9"/>
-    </row>
-    <row r="10" s="8" customFormat="1" spans="1:2">
-      <c r="A10" s="3">
-        <v>11434582801</v>
-      </c>
-      <c r="B10"/>
-    </row>
-    <row r="11" s="8" customFormat="1" spans="1:2">
-      <c r="A11" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="B11"/>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:2">
-      <c r="A12" s="1"/>
+    <row r="12" s="9" customFormat="1" spans="1:2">
+      <c r="A12" s="1">
+        <v>6167222127</v>
+      </c>
       <c r="B12"/>
     </row>
-    <row r="13" s="8" customFormat="1" spans="1:2">
-      <c r="A13" s="1"/>
+    <row r="13" s="9" customFormat="1" spans="1:2">
+      <c r="A13" s="1">
+        <v>4951118353</v>
+      </c>
       <c r="B13"/>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:2">
+    <row r="14" s="9" customFormat="1" spans="1:2">
       <c r="A14" s="1"/>
       <c r="B14"/>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:2">
+    <row r="15" s="9" customFormat="1" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15"/>
     </row>
-    <row r="16" s="8" customFormat="1" spans="1:2">
+    <row r="16" s="9" customFormat="1" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16"/>
     </row>
-    <row r="17" s="8" customFormat="1" spans="1:2">
+    <row r="17" s="9" customFormat="1" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17"/>
     </row>
-    <row r="18" s="8" customFormat="1" spans="1:2">
+    <row r="18" s="9" customFormat="1" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18"/>
     </row>
-    <row r="19" s="8" customFormat="1" spans="1:2">
+    <row r="19" s="9" customFormat="1" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19"/>
     </row>
-    <row r="20" s="8" customFormat="1" spans="1:2">
+    <row r="20" s="9" customFormat="1" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20"/>
     </row>
-    <row r="21" s="8" customFormat="1" spans="1:2">
+    <row r="21" s="9" customFormat="1" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21"/>
     </row>
-    <row r="22" s="8" customFormat="1" spans="1:2">
+    <row r="22" s="9" customFormat="1" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22"/>
     </row>
-    <row r="23" s="8" customFormat="1" spans="1:2">
+    <row r="23" s="9" customFormat="1" spans="1:2">
       <c r="A23" s="2"/>
       <c r="B23"/>
     </row>
-    <row r="24" s="8" customFormat="1" spans="1:2">
+    <row r="24" s="9" customFormat="1" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24"/>
     </row>
-    <row r="25" s="8" customFormat="1" spans="1:2">
+    <row r="25" s="9" customFormat="1" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25"/>
     </row>
-    <row r="26" s="8" customFormat="1" spans="1:2">
+    <row r="26" s="9" customFormat="1" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26"/>
     </row>
-    <row r="27" s="8" customFormat="1" spans="1:2">
-      <c r="A27" s="9"/>
+    <row r="27" s="9" customFormat="1" spans="1:2">
+      <c r="A27" s="10"/>
       <c r="B27"/>
     </row>
-    <row r="28" s="8" customFormat="1" spans="1:2">
+    <row r="28" s="9" customFormat="1" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28"/>
     </row>
-    <row r="29" s="8" customFormat="1" spans="1:2">
+    <row r="29" s="9" customFormat="1" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29"/>
     </row>
-    <row r="30" s="8" customFormat="1" spans="1:2">
+    <row r="30" s="9" customFormat="1" spans="1:2">
       <c r="A30" s="2"/>
       <c r="B30"/>
     </row>
-    <row r="31" s="8" customFormat="1" spans="1:2">
+    <row r="31" s="9" customFormat="1" spans="1:2">
       <c r="A31" s="2"/>
       <c r="B31"/>
     </row>
-    <row r="32" s="8" customFormat="1" spans="1:2">
+    <row r="32" s="9" customFormat="1" spans="1:2">
       <c r="A32" s="2"/>
       <c r="B32"/>
     </row>
-    <row r="33" s="8" customFormat="1" spans="1:2">
+    <row r="33" s="9" customFormat="1" spans="1:2">
       <c r="A33" s="2"/>
       <c r="B33"/>
     </row>
-    <row r="34" s="8" customFormat="1" spans="1:2">
+    <row r="34" s="9" customFormat="1" spans="1:2">
       <c r="A34" s="2"/>
       <c r="B34"/>
     </row>
-    <row r="35" s="8" customFormat="1" spans="1:2">
+    <row r="35" s="9" customFormat="1" spans="1:2">
       <c r="A35" s="2"/>
       <c r="B35"/>
     </row>
-    <row r="36" s="8" customFormat="1" spans="1:2">
+    <row r="36" s="9" customFormat="1" spans="1:2">
       <c r="A36" s="2"/>
       <c r="B36"/>
     </row>
-    <row r="37" s="8" customFormat="1" spans="1:2">
+    <row r="37" s="9" customFormat="1" spans="1:2">
       <c r="A37" s="2"/>
       <c r="B37"/>
     </row>
-    <row r="38" s="8" customFormat="1" spans="1:2">
+    <row r="38" s="9" customFormat="1" spans="1:2">
       <c r="A38" s="2"/>
       <c r="B38"/>
     </row>
-    <row r="39" s="8" customFormat="1" spans="1:2">
+    <row r="39" s="9" customFormat="1" spans="1:2">
       <c r="A39" s="2"/>
       <c r="B39"/>
     </row>
-    <row r="40" s="8" customFormat="1" spans="1:2">
+    <row r="40" s="9" customFormat="1" spans="1:2">
       <c r="A40" s="2"/>
       <c r="B40"/>
     </row>
-    <row r="41" s="8" customFormat="1" spans="1:2">
+    <row r="41" s="9" customFormat="1" spans="1:2">
       <c r="A41" s="2"/>
       <c r="B41"/>
     </row>
-    <row r="42" s="8" customFormat="1" spans="1:2">
+    <row r="42" s="9" customFormat="1" spans="1:2">
       <c r="A42" s="2"/>
       <c r="B42"/>
     </row>
-    <row r="43" s="8" customFormat="1" spans="1:2">
+    <row r="43" s="9" customFormat="1" spans="1:2">
       <c r="A43" s="2"/>
       <c r="B43"/>
     </row>
-    <row r="44" s="8" customFormat="1" spans="1:2">
+    <row r="44" s="9" customFormat="1" spans="1:2">
       <c r="A44" s="2"/>
       <c r="B44"/>
     </row>
-    <row r="45" s="8" customFormat="1" spans="1:2">
+    <row r="45" s="9" customFormat="1" spans="1:2">
       <c r="A45" s="2"/>
       <c r="B45"/>
     </row>
-    <row r="46" s="8" customFormat="1" spans="1:2">
+    <row r="46" s="9" customFormat="1" spans="1:2">
       <c r="A46" s="2"/>
       <c r="B46"/>
     </row>
-    <row r="47" s="8" customFormat="1" spans="1:2">
+    <row r="47" s="9" customFormat="1" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47"/>
     </row>
-    <row r="48" s="8" customFormat="1" spans="1:2">
+    <row r="48" s="9" customFormat="1" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48"/>
     </row>
-    <row r="49" s="8" customFormat="1" spans="1:2">
+    <row r="49" s="9" customFormat="1" spans="1:2">
       <c r="A49" s="2"/>
       <c r="B49"/>
     </row>
-    <row r="50" s="8" customFormat="1" spans="1:2">
+    <row r="50" s="9" customFormat="1" spans="1:2">
       <c r="A50" s="2"/>
       <c r="B50"/>
     </row>
-    <row r="51" s="8" customFormat="1" spans="1:2">
+    <row r="51" s="9" customFormat="1" spans="1:2">
       <c r="A51" s="2"/>
       <c r="B51"/>
     </row>
-    <row r="52" s="8" customFormat="1" spans="1:2">
+    <row r="52" s="9" customFormat="1" spans="1:2">
       <c r="A52" s="2"/>
       <c r="B52"/>
     </row>
-    <row r="53" s="8" customFormat="1" spans="1:2">
+    <row r="53" s="9" customFormat="1" spans="1:2">
       <c r="A53" s="2"/>
       <c r="B53"/>
     </row>
-    <row r="54" s="8" customFormat="1" spans="1:2">
+    <row r="54" s="9" customFormat="1" spans="1:2">
       <c r="A54" s="2"/>
       <c r="B54"/>
     </row>
-    <row r="55" s="8" customFormat="1" spans="1:2">
+    <row r="55" s="9" customFormat="1" spans="1:2">
       <c r="A55" s="2"/>
       <c r="B55"/>
     </row>
-    <row r="56" s="8" customFormat="1" spans="1:2">
+    <row r="56" s="9" customFormat="1" spans="1:2">
       <c r="A56" s="2"/>
       <c r="B56"/>
     </row>
-    <row r="57" s="8" customFormat="1" spans="1:2">
+    <row r="57" s="9" customFormat="1" spans="1:2">
       <c r="A57" s="2"/>
       <c r="B57"/>
     </row>
-    <row r="58" s="8" customFormat="1" spans="1:2">
+    <row r="58" s="9" customFormat="1" spans="1:2">
       <c r="A58" s="2"/>
       <c r="B58"/>
     </row>
@@ -1380,13 +1387,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A14:A20">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2 A8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1420,7 +1427,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1440,7 +1447,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1475,7 +1482,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1485,7 +1492,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1505,7 +1512,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -1605,7 +1612,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1675,7 +1682,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1710,12 +1717,12 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -1735,7 +1742,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -1780,7 +1787,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1810,7 +1817,7 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1825,7 +1832,7 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -1840,7 +1847,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -1889,8 +1896,8 @@
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="10" t="s">
-        <v>18</v>
+      <c r="A98" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -1905,7 +1912,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1940,12 +1947,12 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="4" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="4" t="s">
-        <v>2</v>
+      <c r="A109" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -1959,8 +1966,8 @@
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="4" t="s">
-        <v>3</v>
+      <c r="A112" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2014,237 +2021,237 @@
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="4" t="s">
-        <v>20</v>
+      <c r="A123" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="4">
+      <c r="A124" s="3">
         <v>432621331</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="4">
+      <c r="A125" s="3">
         <v>493936226</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="4">
+      <c r="A126" s="3">
         <v>4277391745</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="4">
+      <c r="A127" s="3">
         <v>947344441</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="4">
+      <c r="A128" s="3">
         <v>359630325</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="4">
+      <c r="A129" s="3">
         <v>1119329980</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="4">
+      <c r="A130" s="3">
         <v>812069862</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="4">
+      <c r="A131" s="3">
         <v>1078528462</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="4">
+      <c r="A132" s="3">
         <v>6579527673</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="4">
+      <c r="A133" s="3">
         <v>27482161619</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="4">
+      <c r="A134" s="3">
         <v>621744185</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="4">
+      <c r="A135" s="3">
         <v>968050527</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="4">
+      <c r="A136" s="3">
         <v>4281272375</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="4">
+      <c r="A137" s="3">
         <v>448182922</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="4" t="s">
-        <v>21</v>
+      <c r="A138" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="4">
+      <c r="A139" s="3">
         <v>42949055728</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="4">
+      <c r="A140" s="3">
         <v>512106660</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="4">
+      <c r="A141" s="3">
         <v>26268349731</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="4">
+      <c r="A142" s="3">
         <v>63577559672</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="4">
+      <c r="A143" s="3">
         <v>63849369908</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="4">
+      <c r="A144" s="3">
         <v>152183964</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="4">
+      <c r="A145" s="3">
         <v>49759885232</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="4">
+      <c r="A146" s="3">
         <v>49366701843</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="4">
+      <c r="A147" s="3">
         <v>27239501863</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="4">
+      <c r="A148" s="3">
         <v>9497311231</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="5">
+      <c r="A149" s="3">
         <v>4987552268</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="5">
+      <c r="A150" s="3">
         <v>266467776</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="5">
+      <c r="A151" s="3">
         <v>956080813</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="5">
+      <c r="A152" s="3">
         <v>3499269458</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="5">
+      <c r="A153" s="3">
         <v>95844646387</v>
       </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="5">
+      <c r="A154" s="3">
         <v>831999359</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="5">
+      <c r="A155" s="3">
         <v>26483210886</v>
       </c>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="5" t="s">
-        <v>22</v>
+      <c r="A156" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="5">
+      <c r="A157" s="3">
         <v>420219798</v>
       </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="5" t="s">
-        <v>23</v>
+      <c r="A158" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="5">
+      <c r="A159" s="3">
         <v>121258041</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="5">
+      <c r="A160" s="3">
         <v>1030176304</v>
       </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="5">
+      <c r="A161" s="3">
         <v>95379423221</v>
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="5">
+      <c r="A162" s="3">
         <v>608319777</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="5">
+      <c r="A163" s="3">
         <v>26502467990</v>
       </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="5">
+      <c r="A164" s="3">
         <v>710203657</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="5">
+      <c r="A165" s="3">
         <v>254778375</v>
       </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="5">
+      <c r="A166" s="3">
         <v>401175349</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="5">
+      <c r="A167" s="3">
         <v>673946666</v>
       </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="5">
+      <c r="A168" s="3">
         <v>113210862</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="5">
+      <c r="A169" s="3">
         <v>908902438</v>
       </c>
     </row>
@@ -2260,7 +2267,7 @@
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -2290,7 +2297,7 @@
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -2305,106 +2312,106 @@
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="6" t="s">
-        <v>27</v>
+      <c r="A182" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="6">
+      <c r="A183" s="5">
         <v>185454787</v>
       </c>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="7" t="s">
-        <v>28</v>
+      <c r="A184" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="6">
+      <c r="A185" s="5">
         <v>946419663</v>
       </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="6" t="s">
-        <v>29</v>
+      <c r="A186" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="6">
+      <c r="A187" s="5">
         <v>983081420</v>
       </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="6" t="s">
-        <v>30</v>
+      <c r="A188" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="6">
+      <c r="A189" s="5">
         <v>486956361</v>
       </c>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190" s="1">
+      <c r="A190" s="7">
         <v>123464203</v>
       </c>
     </row>
     <row r="191" spans="1:1">
-      <c r="A191" s="1">
+      <c r="A191" s="7">
         <v>112233962</v>
       </c>
     </row>
     <row r="192" spans="1:1">
-      <c r="A192" s="1">
+      <c r="A192" s="7">
         <v>112637865</v>
       </c>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193" s="1">
+      <c r="A193" s="7">
         <v>3612824850</v>
       </c>
     </row>
     <row r="194" spans="1:1">
-      <c r="A194" s="1">
+      <c r="A194" s="7">
         <v>6260094048</v>
       </c>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="1">
+      <c r="A195" s="7">
         <v>406757605</v>
       </c>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196" s="1">
+      <c r="A196" s="7">
         <v>1014069758</v>
       </c>
     </row>
     <row r="197" spans="1:1">
-      <c r="A197" s="1">
+      <c r="A197" s="7">
         <v>181070446</v>
       </c>
     </row>
     <row r="198" spans="1:1">
-      <c r="A198" s="1">
+      <c r="A198" s="7">
         <v>874453196</v>
       </c>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>31</v>
+      <c r="A199" s="8" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="1">
+      <c r="A200" s="7">
         <v>6167222127</v>
       </c>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="1">
+      <c r="A201" s="7">
         <v>4951118353</v>
       </c>
     </row>
